--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2016_T2_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2016_T2_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>93</t>
+    <t>89</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>1.352</t>
-  </si>
-  <si>
-    <t>(0.259)</t>
-  </si>
-  <si>
-    <t>5.849</t>
-  </si>
-  <si>
-    <t>(0.780)</t>
-  </si>
-  <si>
-    <t>20.873</t>
-  </si>
-  <si>
-    <t>(4.154)</t>
-  </si>
-  <si>
-    <t>25.638</t>
-  </si>
-  <si>
-    <t>(4.510)</t>
-  </si>
-  <si>
-    <t>1.439</t>
-  </si>
-  <si>
-    <t>(0.260)</t>
-  </si>
-  <si>
-    <t>6.409</t>
-  </si>
-  <si>
-    <t>(0.712)</t>
-  </si>
-  <si>
-    <t>1.488</t>
-  </si>
-  <si>
-    <t>(0.256)</t>
-  </si>
-  <si>
-    <t>0.486</t>
+    <t>1.413</t>
+  </si>
+  <si>
+    <t>(0.269)</t>
+  </si>
+  <si>
+    <t>6.112</t>
+  </si>
+  <si>
+    <t>(0.804)</t>
+  </si>
+  <si>
+    <t>16.484</t>
+  </si>
+  <si>
+    <t>(2.297)</t>
+  </si>
+  <si>
+    <t>21.214</t>
+  </si>
+  <si>
+    <t>(2.841)</t>
+  </si>
+  <si>
+    <t>1.491</t>
+  </si>
+  <si>
+    <t>(0.270)</t>
+  </si>
+  <si>
+    <t>6.674</t>
+  </si>
+  <si>
+    <t>(0.731)</t>
+  </si>
+  <si>
+    <t>1.344</t>
+  </si>
+  <si>
+    <t>(0.221)</t>
+  </si>
+  <si>
+    <t>0.482</t>
   </si>
   <si>
     <t>(0.073)</t>
   </si>
   <si>
-    <t>33.010</t>
-  </si>
-  <si>
-    <t>(5.524)</t>
-  </si>
-  <si>
-    <t>18.457</t>
-  </si>
-  <si>
-    <t>(3.937)</t>
+    <t>27.299</t>
+  </si>
+  <si>
+    <t>(3.551)</t>
+  </si>
+  <si>
+    <t>15.579</t>
+  </si>
+  <si>
+    <t>(2.288)</t>
   </si>
   <si>
     <t>21</t>
@@ -198,7 +198,7 @@
     <t>(8.931)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-0.482</t>
-  </si>
-  <si>
-    <t>-1.897</t>
-  </si>
-  <si>
-    <t>22.896**</t>
-  </si>
-  <si>
-    <t>22.972**</t>
-  </si>
-  <si>
-    <t>-0.362</t>
-  </si>
-  <si>
-    <t>-0.742</t>
-  </si>
-  <si>
-    <t>0.871</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>26.530**</t>
-  </si>
-  <si>
-    <t>20.174**</t>
+    <t>-0.543</t>
+  </si>
+  <si>
+    <t>-2.160</t>
+  </si>
+  <si>
+    <t>27.285***</t>
+  </si>
+  <si>
+    <t>27.396***</t>
+  </si>
+  <si>
+    <t>-0.414</t>
+  </si>
+  <si>
+    <t>-1.007</t>
+  </si>
+  <si>
+    <t>1.015**</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>32.241***</t>
+  </si>
+  <si>
+    <t>23.052***</t>
   </si>
 </sst>
 </file>
